--- a/survey_templates/036_donor_feedback_questionnaire--survey_templates.xlsx
+++ b/survey_templates/036_donor_feedback_questionnaire--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -707,12 +707,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'how_likely_are_you_to_recommend_this_campaign?',_'value':_1}</t>
+          <t>how_likely_are_you_to_recommend_this_campaign?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'How likely are you to recommend this campaign?', 'value': 1}</t>
+          <t>How likely are you to recommend this campaign?</t>
         </is>
       </c>
     </row>
@@ -757,29 +757,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'how_likely_are_you_to_recommend_this_campaign?',_'value':_2}</t>
+          <t>not_likely_at_all</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'How likely are you to recommend this campaign?', 'value': 2}</t>
+          <t>Not likely at all</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>questions_choices</t>
+          <t>contact_method_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'not_likely_at_all',_'value':_3}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Not likely at all', 'value': 3}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'phone',_'value':_'phone'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Phone', 'value': 'phone'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -808,29 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'email',_'value':_'email'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Email', 'value': 'email'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>contact_method_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
